--- a/Assets/StreamingAssets/Chapter/Chapter3.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A107D6-0D71-4B7E-B58A-7DD0C18283FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32C7625-FDD0-46C5-9DD2-033715992FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,1166 +38,1154 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="289">
   <si>
+    <t>病房角落，一对夫妇低声交谈。妇人半卧床上，半边头发已白，脸上刻着病痛的痕迹，眼底却透着微光；丈夫守在床边，虽未受病痛折磨，神情也满是风霜。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>床头挂着幅风景画，小径蜿蜒、绿草如茵，像在诉说外界依旧美好。窗外霓虹交织，车流不息，如生命的卷轴不断向前铺展，直至尽头晕染出诗情画意。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻微的敲门声打破宁静，云叶枫探进头来，手里捧着一束鲜亮的花。花香带着春日暖意，病床上的妇人勉强挤出一丝笑意。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爸！妈！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫努力让语气轻松</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老妈现在感觉怎么样？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少稳定下来了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫蹲在床头，视线有些模糊。但这点模糊挡不住他的目标——工作、赚钱，让妈妈活得舒服些。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>儿子啊，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>母亲用干瘪的手握住他的手，声音轻颤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>妈妈拖累你了……是妈对不起你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫快速甩着脑袋——他从不后悔把自己刚赚的钱拿来给母亲治病，这么多年来都是如此。在发财和治疗之中，他会毫不犹豫地选择后者——这不仅是治疗母亲，而且是对自己的救赎。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他决心不离不弃，无论面对什么困难和挑战，他都会坚定地站在他母亲身边，伴她渡过难关，力尽做到儿子这一职责。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我从来没有感觉我被拖累了——哦对，爸爸你也辛苦了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫说着，顺便在床头的花瓶上再添了一朵花，它的花瓣被霓虹灯染成了淡淡的彩色。花瓣上还挂着几滴晶莹的水珠，闪烁着宝石般的光芒，仿佛是花朵的眼泪，诉说着它的欢喜与忧伤。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这几天我还有任务，你们照顾好自己哈！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫转过身，习惯地抹了一把眼泪，然后走出病房。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;VO</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>妈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒走近，狼人起身转身。漠寒猛地后退——对方竟和自己长得几乎一样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对，你没看错。（眯眼轻笑，上前一步）我就是你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他手中的鱼竿凭空消失</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凑近点。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒本有些抵触，转念想到是梦，便走到他身边。两人刚找地方坐下，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>后悔吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>后悔什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊……（望向远方，目光坚定）我以为刚好赶上了你需要这句话的时刻。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么话？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是我曾对你说的——这是人类自取灭亡的故事，你开启了它，却也是受害者。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是什么意思？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以后你会明白。往后，别恨我，恨你，恨他。世界本就如此，历史总在无限相似地循环推演。你恰巧开启了这个故事，而总会有另一把钥匙，开启相似的篇章……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你想说什么？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>问心无愧，走下去！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠——寒——！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明的喊声将漠寒惊醒。他惊坐起来，与坐在他身上的叶苏明撞了个正着。漠寒被反冲力推回床上，叶苏明捂着头，把响着的手机递给他。漠寒这才发现云叶枫一直在打电话。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弄清今天的安排后，两人简单收拾了一下，赶往 FoxTi活动室。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>听上去挺高深的。什么叫做‘你开启了它，却也是‘受害者’？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不知道，（摇头）莫名其妙的梦。这个梦给我的感觉很不一样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>难道不是？（眯着眼睛，盯）你有多少次把我挤到JumpScare的触发点上了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明偷偷低下头去笑着</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多半怪我——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可不是？要不是你昨晚瞎搞，我能做这梦？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动室里一时没了声音，都没了话题。云叶枫还托着下巴，忽然眼睛一亮，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是不是忘了啥？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啥啊……哦！对了，我还得教你用元核——叶苏明，你来不？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不了不了（摆摆手），你们先弄。让我一个人研究研究活动室的桌子……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>两人离开活动室，往走廊走。漠寒总觉得云叶枫脸上带着点忧郁，猜着大概是为他妈妈。漠寒发现云叶枫似乎总是带着不可磨灭的乐观……靠乐观掩饰或抵抗忧郁——跟叶苏明有点像，又不太一样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿过走廊，他们在元核训练室停下。训练室里散落着几个几何体。这里平时鲜有人来：一来有元核的人本就不多，二来使用者对元核能力的开发不足 1%，大多不知其用途，顶多在关键时刻或缺乏武器时凭它创造些奇迹，实则远不如高科技或充足武器实用。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没来过这地方，真够简陋的。（捂额）跟我想的一样，上一家公司也这德性。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪不得叶苏明从不来。话说这些东西能练出啥？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒找了圈，打开灯和总闸，扫视一圈。房间里有几个靶子和沙袋，一角像射击靶场。墙上方装着些灯条，光都往墙下射。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明明够亮了，还装灯条。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说不定有别的用呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>应该吧。从第一课开始：隔空取物。离了手套也能做到——只要你熟练掌握元核。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>元核的基本知识用讲吗？看你知识面，说不定能省点事。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫学着他的动作，脸都憋红了，浑身肌肉较劲，手上青筋暴起。可任凭他使出吃奶的劲，那圆锥体愣是一动不动，像在嘲讽他。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单个屁！我上次是咋弄出来的？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>脑子？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上次被大水母抓的时候，你脑子里想啥？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我要死了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不对，我问的不是这个。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧，其实我想的是……放手！——然后就莫名其妙炸了。其实我脑补了无数次那破水母‘被迫松手’的样子。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就是关键——现在懂了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哦……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没事吧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一秒，云叶枫嘴角咧得快到耳根</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我操，我他妈成了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒松口气，点头</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫突然觉得头晕，大概是太兴奋了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我头晕，正常不？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你脸都红了，这一下耗不了多少元钛，估计是太激动——要不先歇会儿？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫笑着点头。几分钟后，他试着学漠寒隔空取物，可操控的东西总半途掉下来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我感觉也就这样了。（丧气）这辈子都离不了手套喽！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这事儿……多试试说不定就行——对了，别太累着它，不然你也遭罪。剩下的‘技能’，你自己慢慢挖吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫点头。过了会儿，他想起自己元核粒子是黄色的，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我这元核强度咋样？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>强度（低头想，靠在柱子上）……输出功率中等，就是不知道续航咋样——哦对，叶苏明的元核粒子不是紫色的吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打个比方——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>——你是说叶苏明短小但精悍？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你们刚说啥呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没、没啥。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>两人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们生怕被听见——叶苏明也是要面子的，哪怕他那方面真不是“短小精悍”。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我都听见了！（叉腰）我就元核这方面短小精悍，又不是萎了！——漠寒你说是不是？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是是是。你咋来了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘博士叫队长去 A区 6楼以钛实验室 d1号。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以钛科学还有科学家直接找队员的操作？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫点头，走到门口，给了叶苏明个尴尬的坏笑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>走了，你们先回活动室……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，你看看我是不是‘短小精悍’！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫偷偷摸回门口，看见他们在射击靶场那角。叶苏明用元钛凝出一把火红的弓，拉开弓弦，一支透明箭矢出现。他松手射出，箭却偏了，直奔墙面。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>完了！（报头大喊）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还好，箭矢撞墙的瞬间，墙上的灯条突然变红，箭像蒸发了一样。云叶枫和叶苏明都愣住。叶苏明腿软蹲地上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我……我还以为要赔钱……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒偷偷笑，云叶枫也庆幸没走远，看到了这幕。抛开射歪不谈，叶苏明确实聪明——离得越远，元核凝聚元钛时坍缩概率云的损耗越大，还不是线性增加，是指数级的。这种方式能以较小代价影响远距离，就是受时间和飞行损耗限制。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>另一边，刘宇轩在洁净的实验室里，盯着圆柱形容器中的水母静静站立，等待着来人。窗外不时有车辆与飞鸟掠过，窗边的绿植生机盎然。阳光突然照进来，仪器反光有点晃眼，他调低了灯光。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么才到？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫看着他，刘宇轩神情比平时严肃——他知道这人做实验和不做实验时简直是两个人。再看那水母，正是上次他们带回来的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你……不是在以钛实验室 b1号吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（顿）我一直在这——要是你没听错，估计是你同伴把 d1听成 b1了——我口音有这么怪？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫摇头说没有。他走近水母</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找我啥事？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务报告是你和漠寒写的？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，漠寒写的那部分还行，他来了吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你叫他了？叶苏明没说叫漠寒一起啊。不过你找漠寒干啥？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩无语地笑了声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那小子，听个话都听不全。想请他复现下报告里写的内容。本来不用麻烦他，可公司最近储存的元钛和虚空质快没了——</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是新来的实习生瞎操作，把固定装置关了……好多装置里的元钛和虚空质都结合为反元钛了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫表情惊讶，心想这实习生怕不是已经被炒了——固定在基础维度的元钛和虚空质老贵了，尤其后者。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我试试吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你没戴手套，真行？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫没说话，试着往手上凝聚元钛。手掌旁冒出少量橙黄色粒子，水母的反应和在太空时一样。可奇怪的是，他一停，水母就往固定方向游。刘宇轩挪了挪容器，云叶枫再凝聚元钛，结果还是一样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩推了推眼镜——显然，云叶枫一停，水母就往南游。结合他和漠寒报告里的猜想，刘宇轩觉得以钛科学以北可能有带微量虚空性的东西，或是以南有大量元钛。他还问过上次那个空间站站长，得知水母往南躲的行为是今天才有的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看出啥了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回到元核训练室，云叶枫发现叶苏明和漠寒还在，叶苏明看着累，脸上却挺乐。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘博士叫你干啥去了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没啥，处理点小事。对了，你们听说没？有个实习生关了固定装置，被炒了。当时刘宇轩那脸，红得跟啥似的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那这小子是个人物。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫暗自叹口气，犹豫着走向漠寒，想开口又不知咋说。但想到肩上的担子，还是开了口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咋？</t>
+  </si>
+  <si>
+    <t>你想当队长不？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒懵了，旁边的叶苏明也一脸意外。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>就是你，我打算把队长让给你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能给我吗？（打趣）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你就算了。（正经）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咋突然不想当了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒满脑子问号，这突如其来的担子让他有点懵，跟做梦似的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是这样——队长不能随便请假，得随时待命。我有时候得回家或去医院，批假挺麻烦，虽说周文涵每次都尽力帮我批……我觉得你合适，经验又多，所以想让你当。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>店里开着空调，铜锅里红汤翻滚，热气裹着底料的鲜香扑面而来。刘宇轩常来这儿，说不仅好吃，氛围还好——安静又和谐。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>窗外有小孩打闹，笑声被玻璃挡在外面，漠寒静静看着，一只落单的蝉停在树上，翅膀在夕阳下泛着微光。时间仿佛在这刻停住，喧嚣都远了，只剩这份恬静——可这恬静能持续多久呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他们边吃边聊，漠寒忽然觉得，要是不知道刘宇轩的身份，真想不到他是科学家——他更像个既爱生活又好奇世界奥秘的普通人，实验室里和生活中判若两人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>桌上的铜锅红汤翻滚，热气腾腾，食客们的谈笑声不吵不闹。木质桌椅带点木香，菜盘里的绿叶还挂着水珠，新鲜得很。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩见锅里羊肉不多了，刚想叫服务员，口袋里的手机响了。一看是探测组组长，他把屏幕给三人看了眼，接起电话仔细听着。没多久，三人见他脸上露出惊喜，连说几声“好”就挂了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咋了？实验室又出岔子了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩摇头，顿了顿，像是在考虑该不该说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先吃吧，明天的事明天说，一时半会儿讲不清。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫先是疑惑，随即懂了什么，好奇的神情瞬间变成不耐烦。叶苏明没多想，漠寒却注意到他和刘宇轩神情不对，联想到今天的事，试探</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>要是又有任务，这次钱会多不？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩语气有点沉。云叶枫也叹了口气，他眼中却有一丝光。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩坐在桌前，看着助手刚递来的报告：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以钛科学扫描出北冰洋有四个空间裂口，其中一小的通向一个小世界。北冰洋上空最大的裂缝和这个小裂缝都有巨大的元核能量波动……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>小裂口那边有疑似外星人的建筑，让他震惊的是建筑风格跟地球的人类的很像。观测部扩大扫描后，发现这世界泡只有一颗恒星和一颗行星。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂口那边到底是啥？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他拿起下一份报告，上面赫然写着：世界泡存在可能的深层空间漏洞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这巨大的元核能量波动是什么？是否危险？是否有科研价值？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>接着，他拿起任务建议单，在需求那行写下：探寻元核能量波动的本源。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10点，会议室里 FoxTi全员到齐。周文涵进来没先讲任务，反而盯着漠寒。漠寒左右看了看，有点懵。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫转让队长的申请批了，从现在起，漠寒担任队长。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>她又看向云叶枫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>副队长由你担任。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啥时候冒出个副队长？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我也不知道。三人队里就你们有这职位，队长不在时由副队长接管——队长和副队长决议权同等，意见冲突时，由第三人选择。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒表情有点怪，心想这规定听着不太吉利，而且上层好像也不是真让他指挥。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那副队和主队有啥本质区别？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上面说，副队在某些情况下算临时队长，其他时候跟队员没啥两样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫松了口气。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（凑近漠寒）漠寒，当队长啥感觉？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没感觉。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没感觉就让我来，我比你有感觉。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好了，漠寒是经云叶枫举荐转让才当的队长，他的表现大家有目共睹，确实能担这职责……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒不好意思地点点头。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在说这次任务。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周文涵戴上眼镜，桌面弹出投影</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>北冰洋有处空间裂缝，你们用‘空间爆破仪’炸开，进入那个世界泡，去我们标记的任务点，找元核能量波动的本源，有价值的东西就带回来。里面环境跟地球差不多，裂缝离能量源不远。观测显示，里面可能有虚空兽，没别的生物。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>听着就危险。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是这样，安全第一。任务实在推进不了，或太危险，立马回来——一来爆破的空间会‘愈合’，二来我们也不确定那些材料值不值。装备会给你们配齐，能应付虚空兽和可能突发的虚空场……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会议结束，三人回活动室休整。漠寒靠在沙发上，突然觉得累。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周文涵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你们说裂缝里会有外星人不？（一本正经）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>万一呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>窗外突然暗下来，三人同时看去。天空迅速变黑，厚重的乌云像潮水翻涌。一道银蛇似的闪电划破苍穹，紧接着，轰隆隆的雷声在天地间回荡，仿佛神祇怒吼。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨点像利箭砸在窗上，噼里啪啦响个不停。街上的行人慌忙躲避，有的躲进店铺，有的缩在屋檐下，脸上满是惊慌。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨来了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，胡江老总对你挺好奇，能跟我来一趟不……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。（轻拍他背）周指挥官不是说‘里面可能有虚空兽，除此之外没别的生物’？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goChapter &gt;&gt; story.第四章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>addTag &gt;&gt; 解锁第三章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;◤2064年 7月 21日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨前/病房</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/开关门</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/手机消息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然，云叶枫的裤袋震动起来——是周文涵的电话。周文涵说，FoxTi需要今天上午 10点前到活动室，届时会说明明天的任务。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电话打不通。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他打电话给漠寒。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/电话震动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑场</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;此时，漠寒还在床上酣睡。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨前/竹林</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦里，他走过竹林，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨前/竹林_钓鱼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>来到一汪清澈的湖边。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>空中浮着几层薄雾，水下渔龙潜跃，湖面波光粼粼。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼人收线，端详着钩上的大鱼，满意地笑了笑，随即放生。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨前/竹林_钓鱼2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>White</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>白场</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;Scene</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒和叶苏明的卧室_白天</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/摔倒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi活动室</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫已经在里面等着他们两。今天的会议室有些沉寂，见没人开口提出话题，漠寒讲述了他做的梦。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说道这个，漠寒昨天晚上跟我玩恐怖游戏的时候，老是幻想我会迫害他。（坏笑）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAS过道_白天</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器库_TAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫 &gt;&gt; 淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/射箭</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAS试验室</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/脚步声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>终于，期待的脚步声传来，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>门开了。刘宇轩手插兜，侧身让云叶枫看见容器里的水母。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫像松了口气。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;淡入&gt;&lt;中心文本&gt;傍晚，夕阳把天空染成金红色，云朵像被点燃。城市一角，FoxTi三人和刘宇轩在家人少的火锅店吃饭，刘宇轩换了件灰色短袖。他们坐在靠窗的位置，外面微风带过一丝热浪，混着淡淡的荷花香。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雨前/火锅店</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;叶苏明带头聊起开心事，四人聊到快九点，才各自回家，只有云叶枫去了医院。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>气象观测台</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/写字1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>会议室_TAS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 0.45</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这时，云叶枫的手机响了，是父亲打来的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他接起电话，神情愕然，随即跑出活动室，从迎面走来的刘宇轩身边掠过。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;第二天......</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/挂断电话|音效/跑步声</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒挠了挠头，想到什么东西，嘴角上扬。云叶枫看着漠寒，正疑惑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好像……被元核当移动补给站了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在该它给我打工了！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒抬起左手，对准地上的圆锥体。手心冒出微量蓝色粒子，圆锥体旁也出现同样粒子，下一秒，圆锥体飞到他手里。他在云叶枫眼前晃了晃，又丢回地上</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>很简单。试试？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（叉腰）我以前也这样，后来才发现，用元核不靠肌肉，靠脑子——想想元核的基本性质。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;第二天，阳光透过窗户照进科学家那随性的办公室。墙上挂着实验图表和研究报告，白板上满是彩色笔迹的注解。桌上的小多肉绿油油的，还散落着漫画书和科幻小说，书签露了一角。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩看着他的背影耸耸肩，满脸同情</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/落日余晖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/乌鸦Producer - 萍逢（Piano）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠_未知</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>像有东西在吸引它，或者它在排斥什么。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢了！（收拾仪器）我会向上级汇报，顺便提你想辞队长的事——对了，其实，我觉得小李的事情……真不是你的错。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫脸上不快，沉默。一会儿后，他才缓缓开口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>就算抛开这件事，我家里人需要我陪……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>说着，两人一起出门，刘宇轩抱着一堆文件和他分开，走前叫住他，说晚上请吃火锅。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呃……你这么说，那我就应了。（不好意思地点头）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案_提示 &gt;&gt; 元核|解锁档案 &gt;&gt; 意识流</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案 &gt;&gt; 虚空兽</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁档案 &gt;&gt; 世界泡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测组推测，大裂口直接连虚空。而那个小世界是个&lt;link=profile:[*]世界泡&gt;世界泡&lt;/link&gt;。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>深层空间漏洞？直接通虚空了？任务里怕是会遇到&lt;link=profile:[*]虚空兽&gt;虚空兽&lt;/link&gt;——目前空间的虚空场强不算高，并且稳定，好像不需要严格的抵抗装备。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/Airport Lounge</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>懂点&lt;link=profile:[*]元核 | [*]元虚 | [*]意识流&gt;基本性质&lt;/link&gt;，比如元核是啥、咋驱动的……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫眼睛一亮，像开悟了。他伸手对着个圆柱体，脑子里想了个小爆炸的画面。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一道黄光突然从圆柱体侧边炸开，把它推开几厘米。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫僵在那，漠寒有点担心，走过去摇了摇他。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/风弹_短</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没多久，训练室门开了，叶苏明走进来，看着他们。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/火锅店背景音|音乐/Devonshire Waltz Allegretto</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/When The Wind Blows</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐/When The Wind Blows|音效/雷雨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/过度音效1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒一愣，云叶枫不厚道地笑了。漠寒反应过来，也跟着笑。&lt;br&gt;&lt;size=18&gt;&lt;注释：光子包含的能量越大，光色越往靠近光谱的右边。这里指叶苏明的元核输出功率高却续航差&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>人物</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>对话</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>语音</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>背景/cg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>背景音乐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>转场特效</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘层</t>
   </si>
   <si>
     <t>对话框头像</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>#TAG</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>选项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
   </si>
   <si>
     <t>指令</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>病房角落，一对夫妇低声交谈。妇人半卧床上，半边头发已白，脸上刻着病痛的痕迹，眼底却透着微光；丈夫守在床边，虽未受病痛折磨，神情也满是风霜。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>床头挂着幅风景画，小径蜿蜒、绿草如茵，像在诉说外界依旧美好。窗外霓虹交织，车流不息，如生命的卷轴不断向前铺展，直至尽头晕染出诗情画意。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>轻微的敲门声打破宁静，云叶枫探进头来，手里捧着一束鲜亮的花。花香带着春日暖意，病床上的妇人勉强挤出一丝笑意。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>爸！妈！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫努力让语气轻松</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>老妈现在感觉怎么样？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>至少稳定下来了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫蹲在床头，视线有些模糊。但这点模糊挡不住他的目标——工作、赚钱，让妈妈活得舒服些。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>儿子啊，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>母亲用干瘪的手握住他的手，声音轻颤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>妈妈拖累你了……是妈对不起你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫快速甩着脑袋——他从不后悔把自己刚赚的钱拿来给母亲治病，这么多年来都是如此。在发财和治疗之中，他会毫不犹豫地选择后者——这不仅是治疗母亲，而且是对自己的救赎。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他决心不离不弃，无论面对什么困难和挑战，他都会坚定地站在他母亲身边，伴她渡过难关，力尽做到儿子这一职责。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我从来没有感觉我被拖累了——哦对，爸爸你也辛苦了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫说着，顺便在床头的花瓶上再添了一朵花，它的花瓣被霓虹灯染成了淡淡的彩色。花瓣上还挂着几滴晶莹的水珠，闪烁着宝石般的光芒，仿佛是花朵的眼泪，诉说着它的欢喜与忧伤。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这几天我还有任务，你们照顾好自己哈！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫转过身，习惯地抹了一把眼泪，然后走出病房。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;VO</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>爸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>妈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒走近，狼人起身转身。漠寒猛地后退——对方竟和自己长得几乎一样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>对，你没看错。（眯眼轻笑，上前一步）我就是你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他手中的鱼竿凭空消失</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>凑近点。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒本有些抵触，转念想到是梦，便走到他身边。两人刚找地方坐下，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>后悔吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>后悔什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊……（望向远方，目光坚定）我以为刚好赶上了你需要这句话的时刻。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>什么话？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是我曾对你说的——这是人类自取灭亡的故事，你开启了它，却也是受害者。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这是什么意思？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>以后你会明白。往后，别恨我，恨你，恨他。世界本就如此，历史总在无限相似地循环推演。你恰巧开启了这个故事，而总会有另一把钥匙，开启相似的篇章……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你想说什么？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>问心无愧，走下去！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠——寒——！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明的喊声将漠寒惊醒。他惊坐起来，与坐在他身上的叶苏明撞了个正着。漠寒被反冲力推回床上，叶苏明捂着头，把响着的手机递给他。漠寒这才发现云叶枫一直在打电话。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>弄清今天的安排后，两人简单收拾了一下，赶往 FoxTi活动室。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>听上去挺高深的。什么叫做‘你开启了它，却也是‘受害者’？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不知道，（摇头）莫名其妙的梦。这个梦给我的感觉很不一样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>难道不是？（眯着眼睛，盯）你有多少次把我挤到JumpScare的触发点上了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明偷偷低下头去笑着</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>多半怪我——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可不是？要不是你昨晚瞎搞，我能做这梦？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>活动室里一时没了声音，都没了话题。云叶枫还托着下巴，忽然眼睛一亮，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你是不是忘了啥？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啥啊……哦！对了，我还得教你用元核——叶苏明，你来不？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不了不了（摆摆手），你们先弄。让我一个人研究研究活动室的桌子……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>两人离开活动室，往走廊走。漠寒总觉得云叶枫脸上带着点忧郁，猜着大概是为他妈妈。漠寒发现云叶枫似乎总是带着不可磨灭的乐观……靠乐观掩饰或抵抗忧郁——跟叶苏明有点像，又不太一样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>穿过走廊，他们在元核训练室停下。训练室里散落着几个几何体。这里平时鲜有人来：一来有元核的人本就不多，二来使用者对元核能力的开发不足 1%，大多不知其用途，顶多在关键时刻或缺乏武器时凭它创造些奇迹，实则远不如高科技或充足武器实用。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我没来过这地方，真够简陋的。（捂额）跟我想的一样，上一家公司也这德性。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪不得叶苏明从不来。话说这些东西能练出啥？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒找了圈，打开灯和总闸，扫视一圈。房间里有几个靶子和沙袋，一角像射击靶场。墙上方装着些灯条，光都往墙下射。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明明够亮了，还装灯条。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说不定有别的用呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>应该吧。从第一课开始：隔空取物。离了手套也能做到——只要你熟练掌握元核。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>元核的基本知识用讲吗？看你知识面，说不定能省点事。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫学着他的动作，脸都憋红了，浑身肌肉较劲，手上青筋暴起。可任凭他使出吃奶的劲，那圆锥体愣是一动不动，像在嘲讽他。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>简单个屁！我上次是咋弄出来的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>脑子？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上次被大水母抓的时候，你脑子里想啥？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我要死了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不对，我问的不是这个。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好吧，其实我想的是……放手！——然后就莫名其妙炸了。其实我脑补了无数次那破水母‘被迫松手’的样子。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这就是关键——现在懂了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哦……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没事吧？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一秒，云叶枫嘴角咧得快到耳根</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我操，我他妈成了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒松口气，点头</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫突然觉得头晕，大概是太兴奋了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我头晕，正常不？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你脸都红了，这一下耗不了多少元钛，估计是太激动——要不先歇会儿？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫笑着点头。几分钟后，他试着学漠寒隔空取物，可操控的东西总半途掉下来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我感觉也就这样了。（丧气）这辈子都离不了手套喽！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这事儿……多试试说不定就行——对了，别太累着它，不然你也遭罪。剩下的‘技能’，你自己慢慢挖吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫点头。过了会儿，他想起自己元核粒子是黄色的，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我这元核强度咋样？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>强度（低头想，靠在柱子上）……输出功率中等，就是不知道续航咋样——哦对，叶苏明的元核粒子不是紫色的吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>打个比方——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>——你是说叶苏明短小但精悍？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你们刚说啥呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没、没啥。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>两人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他们生怕被听见——叶苏明也是要面子的，哪怕他那方面真不是“短小精悍”。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我都听见了！（叉腰）我就元核这方面短小精悍，又不是萎了！——漠寒你说是不是？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是是是。你咋来了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘博士叫队长去 A区 6楼以钛实验室 d1号。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>以钛科学还有科学家直接找队员的操作？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫点头，走到门口，给了叶苏明个尴尬的坏笑</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>走了，你们先回活动室……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒，你看看我是不是‘短小精悍’！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫偷偷摸回门口，看见他们在射击靶场那角。叶苏明用元钛凝出一把火红的弓，拉开弓弦，一支透明箭矢出现。他松手射出，箭却偏了，直奔墙面。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>完了！（报头大喊）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还好，箭矢撞墙的瞬间，墙上的灯条突然变红，箭像蒸发了一样。云叶枫和叶苏明都愣住。叶苏明腿软蹲地上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我……我还以为要赔钱……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒偷偷笑，云叶枫也庆幸没走远，看到了这幕。抛开射歪不谈，叶苏明确实聪明——离得越远，元核凝聚元钛时坍缩概率云的损耗越大，还不是线性增加，是指数级的。这种方式能以较小代价影响远距离，就是受时间和飞行损耗限制。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>另一边，刘宇轩在洁净的实验室里，盯着圆柱形容器中的水母静静站立，等待着来人。窗外不时有车辆与飞鸟掠过，窗边的绿植生机盎然。阳光突然照进来，仪器反光有点晃眼，他调低了灯光。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>怎么才到？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫看着他，刘宇轩神情比平时严肃——他知道这人做实验和不做实验时简直是两个人。再看那水母，正是上次他们带回来的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你……不是在以钛实验室 b1号吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（顿）我一直在这——要是你没听错，估计是你同伴把 d1听成 b1了——我口音有这么怪？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫摇头说没有。他走近水母</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找我啥事？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>任务报告是你和漠寒写的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，漠寒写的那部分还行，他来了吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你叫他了？叶苏明没说叫漠寒一起啊。不过你找漠寒干啥？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩无语地笑了声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那小子，听个话都听不全。想请他复现下报告里写的内容。本来不用麻烦他，可公司最近储存的元钛和虚空质快没了——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>主要是新来的实习生瞎操作，把固定装置关了……好多装置里的元钛和虚空质都结合为反元钛了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫表情惊讶，心想这实习生怕不是已经被炒了——固定在基础维度的元钛和虚空质老贵了，尤其后者。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我试试吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你没戴手套，真行？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫没说话，试着往手上凝聚元钛。手掌旁冒出少量橙黄色粒子，水母的反应和在太空时一样。可奇怪的是，他一停，水母就往固定方向游。刘宇轩挪了挪容器，云叶枫再凝聚元钛，结果还是一样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩推了推眼镜——显然，云叶枫一停，水母就往南游。结合他和漠寒报告里的猜想，刘宇轩觉得以钛科学以北可能有带微量虚空性的东西，或是以南有大量元钛。他还问过上次那个空间站站长，得知水母往南躲的行为是今天才有的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看出啥了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>回到元核训练室，云叶枫发现叶苏明和漠寒还在，叶苏明看着累，脸上却挺乐。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘博士叫你干啥去了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没啥，处理点小事。对了，你们听说没？有个实习生关了固定装置，被炒了。当时刘宇轩那脸，红得跟啥似的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那这小子是个人物。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫暗自叹口气，犹豫着走向漠寒，想开口又不知咋说。但想到肩上的担子，还是开了口</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咋？</t>
-  </si>
-  <si>
-    <t>你想当队长不？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒懵了，旁边的叶苏明也一脸意外。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>就是你，我打算把队长让给你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能给我吗？（打趣）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你就算了。（正经）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咋突然不想当了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒满脑子问号，这突如其来的担子让他有点懵，跟做梦似的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是这样——队长不能随便请假，得随时待命。我有时候得回家或去医院，批假挺麻烦，虽说周文涵每次都尽力帮我批……我觉得你合适，经验又多，所以想让你当。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>店里开着空调，铜锅里红汤翻滚，热气裹着底料的鲜香扑面而来。刘宇轩常来这儿，说不仅好吃，氛围还好——安静又和谐。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>窗外有小孩打闹，笑声被玻璃挡在外面，漠寒静静看着，一只落单的蝉停在树上，翅膀在夕阳下泛着微光。时间仿佛在这刻停住，喧嚣都远了，只剩这份恬静——可这恬静能持续多久呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他们边吃边聊，漠寒忽然觉得，要是不知道刘宇轩的身份，真想不到他是科学家——他更像个既爱生活又好奇世界奥秘的普通人，实验室里和生活中判若两人。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>桌上的铜锅红汤翻滚，热气腾腾，食客们的谈笑声不吵不闹。木质桌椅带点木香，菜盘里的绿叶还挂着水珠，新鲜得很。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩见锅里羊肉不多了，刚想叫服务员，口袋里的手机响了。一看是探测组组长，他把屏幕给三人看了眼，接起电话仔细听着。没多久，三人见他脸上露出惊喜，连说几声“好”就挂了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咋了？实验室又出岔子了？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩摇头，顿了顿，像是在考虑该不该说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>先吃吧，明天的事明天说，一时半会儿讲不清。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫先是疑惑，随即懂了什么，好奇的神情瞬间变成不耐烦。叶苏明没多想，漠寒却注意到他和刘宇轩神情不对，联想到今天的事，试探</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>要是又有任务，这次钱会多不？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>会。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩语气有点沉。云叶枫也叹了口气，他眼中却有一丝光。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩坐在桌前，看着助手刚递来的报告：</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>以钛科学扫描出北冰洋有四个空间裂口，其中一小的通向一个小世界。北冰洋上空最大的裂缝和这个小裂缝都有巨大的元核能量波动……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>小裂口那边有疑似外星人的建筑，让他震惊的是建筑风格跟地球的人类的很像。观测部扩大扫描后，发现这世界泡只有一颗恒星和一颗行星。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>裂口那边到底是啥？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他拿起下一份报告，上面赫然写着：世界泡存在可能的深层空间漏洞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这巨大的元核能量波动是什么？是否危险？是否有科研价值？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>接着，他拿起任务建议单，在需求那行写下：探寻元核能量波动的本源。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10点，会议室里 FoxTi全员到齐。周文涵进来没先讲任务，反而盯着漠寒。漠寒左右看了看，有点懵。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫转让队长的申请批了，从现在起，漠寒担任队长。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>她又看向云叶枫</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>副队长由你担任。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啥时候冒出个副队长？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我也不知道。三人队里就你们有这职位，队长不在时由副队长接管——队长和副队长决议权同等，意见冲突时，由第三人选择。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒表情有点怪，心想这规定听着不太吉利，而且上层好像也不是真让他指挥。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那副队和主队有啥本质区别？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>上面说，副队在某些情况下算临时队长，其他时候跟队员没啥两样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫松了口气。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（凑近漠寒）漠寒，当队长啥感觉？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没感觉。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没感觉就让我来，我比你有感觉。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好了，漠寒是经云叶枫举荐转让才当的队长，他的表现大家有目共睹，确实能担这职责……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒不好意思地点点头。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在说这次任务。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周文涵戴上眼镜，桌面弹出投影</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>北冰洋有处空间裂缝，你们用‘空间爆破仪’炸开，进入那个世界泡，去我们标记的任务点，找元核能量波动的本源，有价值的东西就带回来。里面环境跟地球差不多，裂缝离能量源不远。观测显示，里面可能有虚空兽，没别的生物。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>听着就危险。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是这样，安全第一。任务实在推进不了，或太危险，立马回来——一来爆破的空间会‘愈合’，二来我们也不确定那些材料值不值。装备会给你们配齐，能应付虚空兽和可能突发的虚空场……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>会议结束，三人回活动室休整。漠寒靠在沙发上，突然觉得累。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周文涵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你们说裂缝里会有外星人不？（一本正经）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>万一呢？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>窗外突然暗下来，三人同时看去。天空迅速变黑，厚重的乌云像潮水翻涌。一道银蛇似的闪电划破苍穹，紧接着，轰隆隆的雷声在天地间回荡，仿佛神祇怒吼。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>雨点像利箭砸在窗上，噼里啪啦响个不停。街上的行人慌忙躲避，有的躲进店铺，有的缩在屋檐下，脸上满是惊慌。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>雨来了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>行人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒，胡江老总对你挺好奇，能跟我来一趟不……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有。（轻拍他背）周指挥官不是说‘里面可能有虚空兽，除此之外没别的生物’？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goChapter &gt;&gt; story.第四章</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>addTag &gt;&gt; 解锁第三章</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;◤2064年 7月 21日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雨前/病房</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/开关门</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/手机消息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>突然，云叶枫的裤袋震动起来——是周文涵的电话。周文涵说，FoxTi需要今天上午 10点前到活动室，届时会说明明天的任务。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>电话打不通。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他打电话给漠寒。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/电话震动</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑场</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;此时，漠寒还在床上酣睡。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雨前/竹林</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>梦里，他走过竹林，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雨前/竹林_钓鱼</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>来到一汪清澈的湖边。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>空中浮着几层薄雾，水下渔龙潜跃，湖面波光粼粼。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>狼人收线，端详着钩上的大鱼，满意地笑了笑，随即放生。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雨前/竹林_钓鱼2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>White</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>白场</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;Scene</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒和叶苏明的卧室_白天</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/摔倒</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoxTi活动室</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫已经在里面等着他们两。今天的会议室有些沉寂，见没人开口提出话题，漠寒讲述了他做的梦。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说道这个，漠寒昨天晚上跟我玩恐怖游戏的时候，老是幻想我会迫害他。（坏笑）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TAS过道_白天</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器库_TAS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫 &gt;&gt; 淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/射箭</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TAS试验室</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/脚步声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>终于，期待的脚步声传来，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>门开了。刘宇轩手插兜，侧身让云叶枫看见容器里的水母。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫像松了口气。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;淡入&gt;&lt;中心文本&gt;傍晚，夕阳把天空染成金红色，云朵像被点燃。城市一角，FoxTi三人和刘宇轩在家人少的火锅店吃饭，刘宇轩换了件灰色短袖。他们坐在靠窗的位置，外面微风带过一丝热浪，混着淡淡的荷花香。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雨前/火锅店</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;叶苏明带头聊起开心事，四人聊到快九点，才各自回家，只有云叶枫去了医院。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>气象观测台</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/写字1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>会议室_TAS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 0.45</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景明度 &gt;&gt; 1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这时，云叶枫的手机响了，是父亲打来的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他接起电话，神情愕然，随即跑出活动室，从迎面走来的刘宇轩身边掠过。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;第二天......</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/挂断电话|音效/跑步声</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒挠了挠头，想到什么东西，嘴角上扬。云叶枫看着漠寒，正疑惑。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好像……被元核当移动补给站了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在该它给我打工了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒抬起左手，对准地上的圆锥体。手心冒出微量蓝色粒子，圆锥体旁也出现同样粒子，下一秒，圆锥体飞到他手里。他在云叶枫眼前晃了晃，又丢回地上</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>很简单。试试？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>（叉腰）我以前也这样，后来才发现，用元核不靠肌肉，靠脑子——想想元核的基本性质。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;第二天，阳光透过窗户照进科学家那随性的办公室。墙上挂着实验图表和研究报告，白板上满是彩色笔迹的注解。桌上的小多肉绿油油的，还散落着漫画书和科幻小说，书签露了一角。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘宇轩看着他的背影耸耸肩，满脸同情</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/落日余晖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/乌鸦Producer - 萍逢（Piano）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠_未知</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>像有东西在吸引它，或者它在排斥什么。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢了！（收拾仪器）我会向上级汇报，顺便提你想辞队长的事——对了，其实，我觉得小李的事情……真不是你的错。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫脸上不快，沉默。一会儿后，他才缓缓开口</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>就算抛开这件事，我家里人需要我陪……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说着，两人一起出门，刘宇轩抱着一堆文件和他分开，走前叫住他，说晚上请吃火锅。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>呃……你这么说，那我就应了。（不好意思地点头）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案_提示 &gt;&gt; 元核|解锁档案 &gt;&gt; 意识流</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案 &gt;&gt; 虚空兽</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁档案 &gt;&gt; 世界泡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>观测组推测，大裂口直接连虚空。而那个小世界是个&lt;link=profile:[*]世界泡&gt;世界泡&lt;/link&gt;。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>深层空间漏洞？直接通虚空了？任务里怕是会遇到&lt;link=profile:[*]虚空兽&gt;虚空兽&lt;/link&gt;——目前空间的虚空场强不算高，并且稳定，好像不需要严格的抵抗装备。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/Airport Lounge</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>懂点&lt;link=profile:[*]元核 | [*]元虚 | [*]意识流&gt;基本性质&lt;/link&gt;，比如元核是啥、咋驱动的……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫眼睛一亮，像开悟了。他伸手对着个圆柱体，脑子里想了个小爆炸的画面。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>一道黄光突然从圆柱体侧边炸开，把它推开几厘米。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云叶枫僵在那，漠寒有点担心，走过去摇了摇他。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/风弹_短</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没多久，训练室门开了，叶苏明走进来，看着他们。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/火锅店背景音|音乐/Devonshire Waltz Allegretto</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/When The Wind Blows</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐/When The Wind Blows|音效/雷雨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效/过度音效1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wait &gt;&gt; 2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒一愣，云叶枫不厚道地笑了。漠寒反应过来，也跟着笑。&lt;br&gt;&lt;size=18&gt;&lt;注释：光子包含的能量越大，光色越往靠近光谱的右边。这里指叶苏明的元核输出功率高却续航差&gt;</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,13 +1214,6 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1290,7 +1271,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1650,2067 +1631,2067 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>280</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>283</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>284</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>285</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>9</v>
+        <v>286</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>10</v>
+        <v>287</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>11</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C20" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D22" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E22" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D23" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="F23" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D24" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="E24" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="F24" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H29" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="H31" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F32" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H34" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H37" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" t="s">
         <v>48</v>
-      </c>
-      <c r="H40" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
         <v>37</v>
       </c>
-      <c r="B41" t="s">
-        <v>49</v>
-      </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H41" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D42" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E42" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="F42" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D44" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F45" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D58" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F58" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D59" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F59" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" t="s">
         <v>60</v>
-      </c>
-      <c r="B65" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="L67" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C84" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B113" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D113" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G113" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F114" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="G114" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B119" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D120" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="G120" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D121" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F121" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G121" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C122" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C123" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B124" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B126" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B130" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B132" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B133" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B136" t="s">
         <v>118</v>
-      </c>
-      <c r="B136" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B137" t="s">
         <v>30</v>
-      </c>
-      <c r="B137" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B139" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B140" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B144" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B145" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D146" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B147" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D149" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F149" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B150" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B152" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B154" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B155" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B156" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B157" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B158" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B159" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B160" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B161" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B162" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B164" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B165" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B167" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D167" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E167" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D168" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E168" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B169" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D169" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F169" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C173" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B174" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B176" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B178" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B179" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D180" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D181" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E181" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F181" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D182" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E182" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="F182" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D183" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B184" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B185" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="L185" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B187" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B189" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="L189" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B190" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C191" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D191" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D192" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F192" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B193" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B195" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B197" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B199" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B200" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B201" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B202" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B203" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B204" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B205" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B206" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B207" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B208" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B209" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B210" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B211" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D211" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B212" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D212" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F212" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B213" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B215" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E215" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="L215" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B216" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E216" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="L216" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B217" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B218" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B219" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C219" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B220" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C220" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B221" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B222" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D222" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B223" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D223" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F223" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="L223" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L224" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter3.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32C7625-FDD0-46C5-9DD2-033715992FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A107D6-0D71-4B7E-B58A-7DD0C18283FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,54 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="289">
   <si>
+    <t>人物</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景/cg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>转场特效</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话框头像</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#TAG</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>选项</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>病房角落，一对夫妇低声交谈。妇人半卧床上，半边头发已白，脸上刻着病痛的痕迹，眼底却透着微光；丈夫守在床边，虽未受病痛折磨，神情也满是风霜。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1143,49 +1191,13 @@
   <si>
     <t>漠寒一愣，云叶枫不厚道地笑了。漠寒反应过来，也跟着笑。&lt;br&gt;&lt;size=18&gt;&lt;注释：光子包含的能量越大，光色越往靠近光谱的右边。这里指叶苏明的元核输出功率高却续航差&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人物</t>
-  </si>
-  <si>
-    <t>对话</t>
-  </si>
-  <si>
-    <t>语音</t>
-  </si>
-  <si>
-    <t>背景/cg</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>转场特效</t>
-  </si>
-  <si>
-    <t>立绘层</t>
-  </si>
-  <si>
-    <t>对话框头像</t>
-  </si>
-  <si>
-    <t>#TAG</t>
-  </si>
-  <si>
-    <t>选项</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
-  </si>
-  <si>
-    <t>指令</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1214,6 +1226,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1271,7 +1290,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1631,2067 +1650,2067 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>281</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>282</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>283</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>286</v>
+        <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>287</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>288</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E22" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D23" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F23" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D24" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E24" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D25" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F25" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H29" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="H31" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F32" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="H41" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D42" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="L42" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D43" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D44" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F45" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F58" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F59" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="L67" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B72" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B75" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B80" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C84" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B88" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B99" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B101" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B102" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B103" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B104" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C104" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B107" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B108" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B111" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D113" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G113" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D114" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F114" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G114" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B118" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B119" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B120" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D120" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="G120" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D121" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G121" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C122" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B123" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B124" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B125" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B126" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B127" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B128" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B130" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B131" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B132" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B133" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B135" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B136" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B138" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B139" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B140" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B141" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B142" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B143" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B144" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B145" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B146" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D146" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B147" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B148" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B149" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D149" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F149" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B150" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B151" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B152" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B153" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B154" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B155" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B156" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B157" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B158" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B159" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B160" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B161" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B162" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B163" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B164" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B166" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B167" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D167" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E167" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B168" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D168" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E168" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F168" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B169" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D169" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F169" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B170" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B171" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B172" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B173" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C173" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B174" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B175" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B176" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B177" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B178" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B179" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B180" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D180" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D181" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E181" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F181" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D182" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E182" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F182" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D183" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B184" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B185" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="L185" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B186" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B187" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B188" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B189" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L189" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B190" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B191" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C191" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D191" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B192" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D192" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="F192" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B193" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B194" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B196" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B197" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B198" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B199" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B200" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B201" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B202" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B203" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B204" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B205" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B206" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B207" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B208" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B209" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B210" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B211" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D211" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B212" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D212" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F212" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B213" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B214" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B215" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E215" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L215" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B216" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E216" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="L216" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B217" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B218" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B219" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C219" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B220" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C220" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B221" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B222" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D222" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B223" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D223" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F223" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="L223" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L224" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter3.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A107D6-0D71-4B7E-B58A-7DD0C18283FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0F1264-59E8-46ED-8B39-471F9AFF42FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="306">
   <si>
     <t>人物</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -226,18 +226,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>以后你会明白。往后，别恨我，恨你，恨他。世界本就如此，历史总在无限相似地循环推演。你恰巧开启了这个故事，而总会有另一把钥匙，开启相似的篇章……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>你想说什么？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>问心无愧，走下去！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>漠——寒——！</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -254,38 +246,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>听上去挺高深的。什么叫做‘你开启了它，却也是‘受害者’？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不知道，（摇头）莫名其妙的梦。这个梦给我的感觉很不一样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>难道不是？（眯着眼睛，盯）你有多少次把我挤到JumpScare的触发点上了！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明偷偷低下头去笑着</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>多半怪我——</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可不是？要不是你昨晚瞎搞，我能做这梦？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>漠寒</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>活动室里一时没了声音，都没了话题。云叶枫还托着下巴，忽然眼睛一亮，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>你是不是忘了啥？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -294,10 +258,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>不了不了（摆摆手），你们先弄。让我一个人研究研究活动室的桌子……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>两人离开活动室，往走廊走。漠寒总觉得云叶枫脸上带着点忧郁，猜着大概是为他妈妈。漠寒发现云叶枫似乎总是带着不可磨灭的乐观……靠乐观掩饰或抵抗忧郁——跟叶苏明有点像，又不太一样。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -709,10 +669,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>小裂口那边有疑似外星人的建筑，让他震惊的是建筑风格跟地球的人类的很像。观测部扩大扫描后，发现这世界泡只有一颗恒星和一颗行星。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>裂口那边到底是啥？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -721,10 +677,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>这巨大的元核能量波动是什么？是否危险？是否有科研价值？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>接着，他拿起任务建议单，在需求那行写下：探寻元核能量波动的本源。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -857,10 +809,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;中心文本&gt;◤2064年 7月 21日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>暴风雨前/病房</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -961,14 +909,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>云叶枫已经在里面等着他们两。今天的会议室有些沉寂，见没人开口提出话题，漠寒讲述了他做的梦。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>说道这个，漠寒昨天晚上跟我玩恐怖游戏的时候，老是幻想我会迫害他。（坏笑）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>TAS过道_白天</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1133,14 +1073,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>观测组推测，大裂口直接连虚空。而那个小世界是个&lt;link=profile:[*]世界泡&gt;世界泡&lt;/link&gt;。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>深层空间漏洞？直接通虚空了？任务里怕是会遇到&lt;link=profile:[*]虚空兽&gt;虚空兽&lt;/link&gt;——目前空间的虚空场强不算高，并且稳定，好像不需要严格的抵抗装备。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音乐/Airport Lounge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1190,6 +1122,142 @@
   </si>
   <si>
     <t>漠寒一愣，云叶枫不厚道地笑了。漠寒反应过来，也跟着笑。&lt;br&gt;&lt;size=18&gt;&lt;注释：光子包含的能量越大，光色越往靠近光谱的右边。这里指叶苏明的元核输出功率高却续航差&gt;</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云哥，你来不来同学聚会？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;◤2064年 7月 21日 - 云叶枫出租屋中</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好友 · ）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次吧，下次。最近我很忙。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>诶呀，去年也是，前年也是。我说啊云哥，你就不应该老压抑着自己，说来放松放松，聚一聚。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近我过得还好，我妈的情况现在好得多，估计……再过一年就能出院了吧，那时候我再来聚会。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>几句寒暄后，电话挂断。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>卧室里，电脑桌前的椅子背上搭着件外套，椅面上则放着一个半开的背包，露出里面充电线缠绕的电子设备和一些零碎物品，还有几本没签有“刘”字的，没来得及看的科幻短篇小说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一台老旧的二手笔记本电脑放在桌上，略微磨损。电脑还开着，屏幕显示着做完刚做完的任务报告。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫从床上起来，把被子胡乱地掀到一边。昨夜小雨，玻璃上还挂着几道因灰尘而显示的雨痕。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫看着通话记录，有要么就通话几分钟，有要么直接拒绝的。他一下子重躺在床上，自嘲：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是要变成透明人吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老实说，云叶枫渴望参加同学聚会，甚至想腾出时间去社交。现在的他早就和公司、出租屋和医院三点成三角，稳定不可破了，就连谈个女朋友的时间都没有。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧，不经风雨，哪来彩虹呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在是下旬，再过十天就要缴医药费了，而云叶枫感觉明明昨天才缴完费。这个月的医疗账单还放在电脑桌上，费用抵上了他一半的工资，账单旁边散落几张欠条，上面划了几笔，刚刚还清。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>云叶枫吸了口气，坐起来，穿上床上的衣服，稍加洗漱，晾好昨天换下的内衣内裤就出门了。来到出租屋下，窗外明媚的阳光洒在他的脸上，云叶枫张开双臂享受阳光，心里顿时一阵惬意。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;新的一天，加油吧！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他没有买早餐，而是径直地往靠近以钛科学的市中心的人民医院赶去。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以后你会明白。往后，别恨我，恨你，恨他。世界本就如此，历史总在无限相似地循环推演。你在阡陌中往返，找到一丝不存在的可能……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>算是自我安慰吧——问心无愧，走下去！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>到达活动室，云叶枫已经在里面等着他们俩。云叶枫正在用手机浏览着漠寒的小说，脸上不亦乐乎。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒？小说写的不错啊，考虑出版吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒愣了一下，没想到云叶枫真的会看他写的小说</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>真的吗？谢谢！——不过……实际上没有出版社要我这本小说……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能对我这种书迷来说刚刚好吧。顺便一提，刘宇轩的房间里有一面墙放满了科幻小说——如果你不介意的话我还能给刘宇轩看看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>别、别……等哪天出版了再说吧！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好啊，你说的！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动室里一时没了声音，都没了话题。云叶枫托着下巴，忽然眼睛一亮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不了不了，你们先弄。让我一个人研究研究活动室的桌子……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测组推测，大裂口直接连虚空。而那个小世界是个&lt;link=profile:[*]世界泡&gt;世界泡&lt;/link&gt;——数据显示，这个世界泡处于不稳定状态。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过周文涵对现有的数据建模还原，小裂口的另一端疑似存在外星人的建筑，最让他们震惊的是建筑风格跟地球的人类的很像。更神秘的是，观测部扩大扫描后，发现这世界泡只有一颗恒星和一颗行星。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘宇轩依稀记得那天周文涵在观测小组内踱步，嘴上一遍遍说着“这怎么可能”。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>深层空间漏洞？直接通虚空了？目前人类只在太阳系范围的虚空内发现过虚空兽，在无穷远的另一方天地上，是否会存在&lt;link=profile:[*]虚空兽&gt;虚空兽&lt;/link&gt;呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>而且，目前空间的虚空场强不算高，并且稳定，好像不需要严格的抵抗装备。不过，这巨大的元核能量波动是什么？是否危险？是否有科研价值？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1639,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L224"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1691,237 +1759,267 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="L2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F3" t="s">
-        <v>207</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>210</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="B5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="B8" t="s">
-        <v>17</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="B9" t="s">
-        <v>18</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="B10" t="s">
-        <v>19</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" t="s">
-        <v>211</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>214</v>
+      <c r="A21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="B22" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E22" t="s">
-        <v>262</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="B23" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" t="s">
-        <v>208</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F23" t="s">
-        <v>216</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="B24" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E24" t="s">
-        <v>263</v>
-      </c>
-      <c r="F24" t="s">
-        <v>216</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="B25" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" t="s">
-        <v>220</v>
-      </c>
-      <c r="F25" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1929,18 +2027,15 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1948,679 +2043,691 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" t="s">
-        <v>220</v>
-      </c>
-      <c r="H31" t="s">
-        <v>264</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" t="s">
+        <v>248</v>
+      </c>
+      <c r="F40" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
+        <v>207</v>
+      </c>
+      <c r="H47" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
         <v>38</v>
       </c>
-      <c r="D32" t="s">
-        <v>224</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="D48" t="s">
+        <v>211</v>
+      </c>
+      <c r="F48" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="H52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="H54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>290</v>
+      </c>
+      <c r="H55" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="H56" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>291</v>
+      </c>
+      <c r="D57" t="s">
+        <v>211</v>
+      </c>
+      <c r="H57" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" t="s">
+        <v>269</v>
+      </c>
+      <c r="D58" t="s">
+        <v>212</v>
+      </c>
+      <c r="E58" t="s">
+        <v>248</v>
+      </c>
+      <c r="F58" t="s">
+        <v>213</v>
+      </c>
+      <c r="L58" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>39</v>
-      </c>
-      <c r="H33" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" t="s">
-        <v>40</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="D60" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" t="s">
+        <v>217</v>
+      </c>
+      <c r="E61" t="s">
+        <v>259</v>
+      </c>
+      <c r="F61" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B69" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B73" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" t="s">
+        <v>218</v>
+      </c>
+      <c r="F74" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" t="s">
+        <v>219</v>
+      </c>
+      <c r="F75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="H38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" t="s">
-        <v>48</v>
-      </c>
-      <c r="H40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" t="s">
-        <v>224</v>
-      </c>
-      <c r="H41" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C42" t="s">
-        <v>286</v>
-      </c>
-      <c r="D42" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" t="s">
-        <v>226</v>
-      </c>
-      <c r="L42" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" t="s">
-        <v>215</v>
-      </c>
-      <c r="D43" t="s">
-        <v>228</v>
-      </c>
-      <c r="E43" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C44" t="s">
-        <v>229</v>
-      </c>
-      <c r="D44" t="s">
-        <v>228</v>
-      </c>
-      <c r="E44" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="s">
-        <v>230</v>
-      </c>
-      <c r="E45" t="s">
-        <v>276</v>
-      </c>
-      <c r="F45" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="B81" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>260</v>
+      </c>
+      <c r="L83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" t="s">
         <v>64</v>
       </c>
-      <c r="D57" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" t="s">
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
         <v>65</v>
       </c>
-      <c r="D58" t="s">
-        <v>233</v>
-      </c>
-      <c r="F58" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
         <v>66</v>
       </c>
-      <c r="D59" t="s">
-        <v>234</v>
-      </c>
-      <c r="F59" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" t="s">
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B95" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" t="s">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B64" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B67" t="s">
-        <v>277</v>
-      </c>
-      <c r="L67" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B68" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B70" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B83" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B84" t="s">
-        <v>279</v>
-      </c>
-      <c r="C84" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B85" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B86" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B87" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B88" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B89" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B90" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B92" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B94" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B95" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B96" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>262</v>
+      </c>
+      <c r="C100" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -2628,74 +2735,71 @@
         <v>29</v>
       </c>
       <c r="B103" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
-        <v>282</v>
-      </c>
-      <c r="C104" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -2703,478 +2807,481 @@
         <v>29</v>
       </c>
       <c r="B112" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B114" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B115" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B116" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B118" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B119" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B121" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B123" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B124" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B125" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B126" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B127" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B129" t="s">
+        <v>99</v>
+      </c>
+      <c r="D129" t="s">
+        <v>219</v>
+      </c>
+      <c r="G129" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D130" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" t="s">
+        <v>194</v>
+      </c>
+      <c r="G130" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B131" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" t="s">
+        <v>101</v>
+      </c>
+      <c r="C132" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B133" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B134" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B135" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" t="s">
+        <v>105</v>
+      </c>
+      <c r="D136" t="s">
+        <v>218</v>
+      </c>
+      <c r="G136" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" t="s">
+        <v>222</v>
+      </c>
+      <c r="F137" t="s">
+        <v>203</v>
+      </c>
+      <c r="G137" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B138" t="s">
+        <v>224</v>
+      </c>
+      <c r="C138" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" t="s">
+        <v>225</v>
+      </c>
+      <c r="C139" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B113" t="s">
+      <c r="B140" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" t="s">
         <v>109</v>
       </c>
-      <c r="D113" t="s">
-        <v>234</v>
-      </c>
-      <c r="G113" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D114" t="s">
-        <v>233</v>
-      </c>
-      <c r="F114" t="s">
-        <v>207</v>
-      </c>
-      <c r="G114" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B115" t="s">
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B142" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B116" t="s">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" t="s">
         <v>111</v>
       </c>
-      <c r="C116" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B117" t="s">
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B118" t="s">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B145" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B146" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B147" t="s">
         <v>115</v>
       </c>
-      <c r="D120" t="s">
-        <v>233</v>
-      </c>
-      <c r="G120" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B121" t="s">
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B148" t="s">
         <v>116</v>
       </c>
-      <c r="D121" t="s">
-        <v>237</v>
-      </c>
-      <c r="F121" t="s">
-        <v>216</v>
-      </c>
-      <c r="G121" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B122" t="s">
-        <v>239</v>
-      </c>
-      <c r="C122" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B123" t="s">
-        <v>240</v>
-      </c>
-      <c r="C123" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="3" t="s">
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" t="s">
         <v>118</v>
       </c>
-      <c r="B124" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B125" t="s">
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B151" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B126" t="s">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B152" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B127" t="s">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B153" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B128" t="s">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B155" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B129" t="s">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B156" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B130" t="s">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B157" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B131" t="s">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B158" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B132" t="s">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B159" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B133" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B134" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B135" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B136" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B137" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B138" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B139" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B140" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B141" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B142" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B143" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B144" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B145" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B146" t="s">
-        <v>267</v>
-      </c>
-      <c r="D146" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B147" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B148" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B149" t="s">
-        <v>137</v>
-      </c>
-      <c r="D149" t="s">
-        <v>234</v>
-      </c>
-      <c r="F149" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B150" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B151" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B152" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B153" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B154" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B155" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B156" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B157" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B158" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B159" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B160" t="s">
-        <v>148</v>
+        <v>250</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B161" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B162" t="s">
-        <v>150</v>
+        <v>252</v>
+      </c>
+      <c r="D162" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B163" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B164" t="s">
-        <v>152</v>
+        <v>254</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B165" t="s">
-        <v>270</v>
+        <v>127</v>
+      </c>
+      <c r="D165" t="s">
+        <v>219</v>
+      </c>
+      <c r="F165" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B166" t="s">
-        <v>241</v>
+        <v>128</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
@@ -3182,535 +3289,668 @@
         <v>30</v>
       </c>
       <c r="B167" t="s">
-        <v>153</v>
-      </c>
-      <c r="D167" t="s">
-        <v>234</v>
-      </c>
-      <c r="E167" t="s">
-        <v>276</v>
+        <v>129</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B168" t="s">
-        <v>242</v>
-      </c>
-      <c r="D168" t="s">
-        <v>208</v>
-      </c>
-      <c r="E168" t="s">
-        <v>283</v>
-      </c>
-      <c r="F168" t="s">
-        <v>216</v>
+        <v>130</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="B169" t="s">
-        <v>154</v>
-      </c>
-      <c r="D169" t="s">
-        <v>243</v>
-      </c>
-      <c r="F169" t="s">
-        <v>207</v>
+        <v>131</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="B170" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="B171" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="B172" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B173" t="s">
-        <v>158</v>
-      </c>
-      <c r="C173" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B174" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B175" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="B176" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B177" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B178" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B179" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B180" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B181" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B182" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B183" t="s">
+        <v>143</v>
+      </c>
+      <c r="D183" t="s">
+        <v>219</v>
+      </c>
+      <c r="E183" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B184" t="s">
+        <v>227</v>
+      </c>
+      <c r="D184" t="s">
+        <v>195</v>
+      </c>
+      <c r="E184" t="s">
+        <v>266</v>
+      </c>
+      <c r="F184" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B185" t="s">
+        <v>144</v>
+      </c>
+      <c r="D185" t="s">
+        <v>228</v>
+      </c>
+      <c r="F185" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B186" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B187" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B188" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B189" t="s">
+        <v>148</v>
+      </c>
+      <c r="C189" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B190" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B191" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B192" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B193" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B194" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B195" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A196" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B196" t="s">
+        <v>155</v>
+      </c>
+      <c r="D196" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B197" t="s">
+        <v>229</v>
+      </c>
+      <c r="D197" t="s">
+        <v>195</v>
+      </c>
+      <c r="E197" t="s">
+        <v>266</v>
+      </c>
+      <c r="F197" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B198" t="s">
+        <v>245</v>
+      </c>
+      <c r="D198" t="s">
+        <v>195</v>
+      </c>
+      <c r="E198" t="s">
+        <v>267</v>
+      </c>
+      <c r="F198" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
+        <v>156</v>
+      </c>
+      <c r="D199" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>301</v>
+      </c>
+      <c r="L201" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B203" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A204" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B204" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A205" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B205" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A206" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B206" t="s">
+        <v>304</v>
+      </c>
+      <c r="L206" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B207" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A208" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B208" t="s">
+        <v>160</v>
+      </c>
+      <c r="C208" t="s">
+        <v>231</v>
+      </c>
+      <c r="D208" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B209" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B177" t="s">
+      <c r="D209" t="s">
+        <v>232</v>
+      </c>
+      <c r="F209" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B210" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B178" t="s">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B211" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B179" t="s">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B212" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B180" t="s">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B213" t="s">
         <v>165</v>
       </c>
-      <c r="D180" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B181" t="s">
-        <v>244</v>
-      </c>
-      <c r="D181" t="s">
-        <v>208</v>
-      </c>
-      <c r="E181" t="s">
-        <v>283</v>
-      </c>
-      <c r="F181" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B182" t="s">
-        <v>260</v>
-      </c>
-      <c r="D182" t="s">
-        <v>208</v>
-      </c>
-      <c r="E182" t="s">
-        <v>284</v>
-      </c>
-      <c r="F182" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B183" t="s">
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B214" t="s">
         <v>166</v>
       </c>
-      <c r="D183" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B184" t="s">
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B215" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B185" t="s">
-        <v>274</v>
-      </c>
-      <c r="L185" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B186" t="s">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B216" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B187" t="s">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B217" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A188" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B188" t="s">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B218" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B189" t="s">
-        <v>275</v>
-      </c>
-      <c r="L189" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B190" t="s">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B219" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A191" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B191" t="s">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B220" t="s">
         <v>172</v>
       </c>
-      <c r="C191" t="s">
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B221" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B222" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B223" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B224" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B225" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B226" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B227" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B228" t="s">
+        <v>180</v>
+      </c>
+      <c r="D228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B229" t="s">
+        <v>181</v>
+      </c>
+      <c r="D229" t="s">
+        <v>217</v>
+      </c>
+      <c r="F229" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B230" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A231" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B231" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A232" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B232" t="s">
+        <v>184</v>
+      </c>
+      <c r="E232" t="s">
+        <v>267</v>
+      </c>
+      <c r="L232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B233" t="s">
+        <v>185</v>
+      </c>
+      <c r="E233" t="s">
+        <v>268</v>
+      </c>
+      <c r="L233" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A234" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B234" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A235" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B235" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A236" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B236" t="s">
+        <v>235</v>
+      </c>
+      <c r="C236" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B237" t="s">
+        <v>236</v>
+      </c>
+      <c r="C237" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A238" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B238" t="s">
         <v>246</v>
       </c>
-      <c r="D191" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B192" t="s">
-        <v>173</v>
-      </c>
-      <c r="D192" t="s">
-        <v>247</v>
-      </c>
-      <c r="F192" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B193" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B194" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B195" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B196" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B197" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B198" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B199" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B200" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B201" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B202" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B203" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B204" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B205" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B206" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B207" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B208" t="s">
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A239" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B239" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A209" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B209" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A210" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B210" t="s">
+      <c r="D239" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B240" t="s">
+        <v>237</v>
+      </c>
+      <c r="D240" t="s">
+        <v>195</v>
+      </c>
+      <c r="F240" t="s">
+        <v>203</v>
+      </c>
+      <c r="L240" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="241" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L241" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A211" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B211" t="s">
-        <v>192</v>
-      </c>
-      <c r="D211" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A212" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B212" t="s">
-        <v>193</v>
-      </c>
-      <c r="D212" t="s">
-        <v>230</v>
-      </c>
-      <c r="F212" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A213" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B213" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A214" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B214" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A215" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B215" t="s">
-        <v>196</v>
-      </c>
-      <c r="E215" t="s">
-        <v>284</v>
-      </c>
-      <c r="L215" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A216" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B216" t="s">
-        <v>197</v>
-      </c>
-      <c r="E216" t="s">
-        <v>285</v>
-      </c>
-      <c r="L216" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A217" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B217" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A218" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B218" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A219" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B219" t="s">
-        <v>250</v>
-      </c>
-      <c r="C219" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B220" t="s">
-        <v>251</v>
-      </c>
-      <c r="C220" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A221" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B221" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A222" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B222" t="s">
-        <v>201</v>
-      </c>
-      <c r="D222" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A223" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B223" t="s">
-        <v>252</v>
-      </c>
-      <c r="D223" t="s">
-        <v>208</v>
-      </c>
-      <c r="F223" t="s">
-        <v>216</v>
-      </c>
-      <c r="L223" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L224" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter3.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0F1264-59E8-46ED-8B39-471F9AFF42FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFC1362-56D7-4129-AF8E-70CBF1A438F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="9945" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
